--- a/reports/二级子公司D_利润表_2026-06.xlsx
+++ b/reports/二级子公司D_利润表_2026-06.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>88211736</v>
+        <v>89955655</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>86255323</v>
+        <v>86103479</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>486915549</v>
+        <v>487404230</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>296889</v>
+        <v>295295</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1679056</v>
+        <v>1678946</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>256139</v>
+        <v>253347</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1438724</v>
+        <v>1438211</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>211870</v>
+        <v>211506</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1198509</v>
+        <v>1197844</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>189913</v>
+        <v>190807</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1079137</v>
+        <v>1077630</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>106441</v>
+        <v>106270</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>599644</v>
+        <v>598581</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>85244</v>
+        <v>85204</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>479470</v>
+        <v>478907</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>87065240</v>
+        <v>88813226</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>85108827</v>
+        <v>84961050</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4801307</v>
+        <v>4800355</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>26979564</v>
+        <v>26977785</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>371634</v>
+        <v>372819</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>2097409</v>
+        <v>2099519</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>632722</v>
+        <v>637736</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>3596647</v>
+        <v>3600887</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>76473059</v>
+        <v>76337191</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>431759805</v>
+        <v>432224579</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1280222</v>
+        <v>1269240</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>7192911</v>
+        <v>7203915</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>423070</v>
+        <v>422290</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>2397082</v>
+        <v>2400752</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2112063</v>
+        <v>2109320</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>11991485</v>
+        <v>11998439</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>532880</v>
+        <v>527347</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>2998055</v>
+        <v>2997873</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1915444</v>
+        <v>1900474</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>10787310</v>
+        <v>10785722</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>40969</v>
+        <v>41081</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>247191</v>
+        <v>247029</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1145229</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>6465550</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>765392</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>4309781</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>57984166</v>
+        <v>62275472</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>52023491</v>
+        <v>52188422</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>51064114</v>
+        <v>51228487</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>287833656</v>
+        <v>287610567</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>959377</v>
+        <v>959935</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>5394193</v>
+        <v>5396001</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1916868</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>10798302</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>612029</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>3457022</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>381558</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2161161</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>456795</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>2593367</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>341990</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1944517</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>227793</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1295738</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>189861</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1079145</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>899522</v>
+        <v>897636</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>5093734</v>
+        <v>5092859</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>686161</v>
+        <v>687802</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>3897113</v>
+        <v>3892506</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>532654</v>
+        <v>530377</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>2998125</v>
+        <v>2993212</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4045810</v>
+        <v>4040834</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>22773735</v>
+        <v>22746101</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>153673</v>
+        <v>159835</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>926924</v>
+        <v>898014</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>329016</v>
+        <v>331474</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1978347</v>
+        <v>1975516</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>373006</v>
+        <v>331474</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2224697</v>
+        <v>1975516</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>41191</v>
+        <v>41415</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>247111</v>
+        <v>247191</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>167449</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1001692</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>334594</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1890645</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>111097</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>668310</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>83131</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>501265</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>138321</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>835299</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>474551</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>2699258</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>73740</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>445088</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>55378</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>333624</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>92489</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>555746</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>64903</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>388872</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>46472</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>277718</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>37251</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>222189</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>27971</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>166692</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>29081074</v>
+        <v>27698808</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>33399521</v>
+        <v>30869569</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>191583</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1079979</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>46392</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>278395</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>72129</v>
+        <v>71983</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>432441</v>
+        <v>433174</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>29008945</v>
+        <v>27818408</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2579143</v>
+        <v>2561106</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>15455057</v>
+        <v>15467884</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>26429802</v>
+        <v>25257302</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>26429802</v>
+        <v>25257302</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>26429802</v>
+        <v>25257302</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>26429802</v>
+        <v>25257302</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>26429802</v>
+        <v>25257302</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
